--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251106_201538.xlsx
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
